--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_65279_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_65279_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R36d30f1f1850458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc765b2bc876049fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2071</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2129</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2125</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_65279_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_65279_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc765b2bc876049fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6ef7f82aa83140ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1813</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1842</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1863</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1933</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1958</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1904</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2052</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2148</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2138</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2248</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
